--- a/cet4/result/63_体育女神_田径冠军的逆袭路/63_体育女神_田径冠军的逆袭路_学习版.xlsx
+++ b/cet4/result/63_体育女神_田径冠军的逆袭路/63_体育女神_田径冠军的逆袭路_学习版.xlsx
@@ -397,493 +397,479 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>title</v>
       </c>
       <c r="B2" t="str">
-        <v>title</v>
+        <v>/ˈtaɪtl/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>冠军</v>
       </c>
-      <c r="D2" t="str">
-        <v>title(冠军)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>hobby</v>
       </c>
       <c r="B3" t="str">
-        <v>hobby</v>
+        <v>/ˈhɑːbi/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>嗜好</v>
       </c>
-      <c r="D3" t="str">
-        <v>hobby(嗜好)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>divorce</v>
       </c>
       <c r="B4" t="str">
-        <v>divorce</v>
+        <v>/dɪˈvɔːrs/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D4" t="str">
         <v>离婚</v>
       </c>
-      <c r="D4" t="str">
-        <v>divorce(离婚)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>primarily</v>
       </c>
       <c r="B5" t="str">
-        <v>primarily</v>
+        <v>/praɪˈmerəli/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>主要地</v>
       </c>
-      <c r="D5" t="str">
-        <v>primarily(主要地)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>endure</v>
       </c>
       <c r="B6" t="str">
-        <v>endure</v>
+        <v>/ɪnˈdʊr/</v>
       </c>
       <c r="C6" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>忍耐</v>
       </c>
-      <c r="D6" t="str">
-        <v>endure(忍耐)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>idiom</v>
       </c>
       <c r="B7" t="str">
-        <v>idiom</v>
+        <v>/ˈɪdiəm/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>成语</v>
       </c>
-      <c r="D7" t="str">
-        <v>idiom(成语)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>loudspeaker</v>
       </c>
       <c r="B8" t="str">
-        <v>loudspeaker</v>
+        <v>/ˌlaʊdˈspiːkər/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>喇叭</v>
       </c>
-      <c r="D8" t="str">
-        <v>loudspeaker(喇叭)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>middle</v>
       </c>
       <c r="B9" t="str">
-        <v>middle</v>
+        <v>/ˈmɪdl/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>中间</v>
       </c>
-      <c r="D9" t="str">
-        <v>middle(中间)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>purpose</v>
       </c>
       <c r="B10" t="str">
-        <v>purpose</v>
+        <v>/ˈpɜːrpəs/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D10" t="str">
         <v>目的</v>
       </c>
-      <c r="D10" t="str">
-        <v>purpose(目的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>preface</v>
       </c>
       <c r="B11" t="str">
-        <v>preface</v>
+        <v>/ˈprefəs/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>前言</v>
       </c>
-      <c r="D11" t="str">
-        <v>preface(前言)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>attractive</v>
       </c>
       <c r="B12" t="str">
-        <v>attractive</v>
+        <v>/əˈtræktɪv/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>吸引人的</v>
       </c>
-      <c r="D12" t="str">
-        <v>attractive(吸引人的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>mad</v>
       </c>
       <c r="B13" t="str">
-        <v>mad</v>
+        <v>/mæd/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>疯狂的</v>
       </c>
-      <c r="D13" t="str">
-        <v>mad(疯狂的)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>lung</v>
       </c>
       <c r="B14" t="str">
-        <v>lung</v>
+        <v>/lʌŋ/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>肺</v>
       </c>
-      <c r="D14" t="str">
-        <v>lung(肺)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>your</v>
       </c>
       <c r="B15" t="str">
-        <v>your</v>
+        <v>/jʊr,jər/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D15" t="str">
         <v>你的</v>
       </c>
-      <c r="D15" t="str">
-        <v>your(你的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>physics</v>
       </c>
       <c r="B16" t="str">
-        <v>physics</v>
+        <v>/ˈfɪzɪks/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>物理学</v>
       </c>
-      <c r="D16" t="str">
-        <v>physics(物理学)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>Latin</v>
       </c>
       <c r="B17" t="str">
-        <v>Latin</v>
+        <v>/ˈlætn/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>拉丁语</v>
       </c>
-      <c r="D17" t="str">
-        <v>Latin(拉丁语)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>companion</v>
       </c>
       <c r="B18" t="str">
-        <v>companion</v>
+        <v>/kəmˈpænjən/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>同伴</v>
       </c>
-      <c r="D18" t="str">
-        <v>companion(同伴)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>bronze</v>
       </c>
       <c r="B19" t="str">
-        <v>bronze</v>
+        <v>/brɑːnz/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>青铜</v>
       </c>
-      <c r="D19" t="str">
-        <v>bronze(青铜)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>television</v>
       </c>
       <c r="B20" t="str">
-        <v>television</v>
+        <v>/ˈtelɪvɪʒn/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>电视</v>
       </c>
-      <c r="D20" t="str">
-        <v>television(电视)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>campaign</v>
       </c>
       <c r="B21" t="str">
-        <v>campaign</v>
+        <v>/kæmˈpeɪn/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D21" t="str">
         <v>运动</v>
       </c>
-      <c r="D21" t="str">
-        <v>campaign(运动)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>character</v>
       </c>
       <c r="B22" t="str">
-        <v>primarily</v>
+        <v>/ˈkærəktər/</v>
       </c>
       <c r="C22" t="str">
-        <v>主要地</v>
+        <v>n./vt.</v>
       </c>
       <c r="D22" t="str">
-        <v>primarily(主要地)📢</v>
+        <v>性格</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>geometry</v>
       </c>
       <c r="B23" t="str">
-        <v>character</v>
+        <v>/dʒiˈɑːmətri/</v>
       </c>
       <c r="C23" t="str">
-        <v>性格</v>
+        <v>n.</v>
       </c>
       <c r="D23" t="str">
-        <v>character(性格)📢</v>
+        <v>几何</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>sharply</v>
       </c>
       <c r="B24" t="str">
-        <v>geometry</v>
+        <v>/ˈʃɑːrpli/</v>
       </c>
       <c r="C24" t="str">
-        <v>几何</v>
+        <v>v./adv.</v>
       </c>
       <c r="D24" t="str">
-        <v>geometry(几何)📢</v>
+        <v>急剧地</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>transform</v>
       </c>
       <c r="B25" t="str">
-        <v>sharply</v>
+        <v>/trænsˈfɔːrm/</v>
       </c>
       <c r="C25" t="str">
-        <v>急剧地</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D25" t="str">
-        <v>sharply(急剧地)📢</v>
+        <v>改变</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>voluntary</v>
       </c>
       <c r="B26" t="str">
-        <v>transform</v>
+        <v>/ˈvɑːlənteri/</v>
       </c>
       <c r="C26" t="str">
-        <v>改变</v>
+        <v>n./adj.</v>
       </c>
       <c r="D26" t="str">
-        <v>transform(改变)📢</v>
+        <v>自愿的</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>comb</v>
       </c>
       <c r="B27" t="str">
-        <v>voluntary</v>
+        <v>/koʊm/</v>
       </c>
       <c r="C27" t="str">
-        <v>自愿的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>voluntary(自愿的)📢</v>
+        <v>梳子</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>focus</v>
       </c>
       <c r="B28" t="str">
-        <v>comb</v>
+        <v>/ˈfoʊkəs/</v>
       </c>
       <c r="C28" t="str">
-        <v>梳子</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D28" t="str">
-        <v>comb(梳子)📢</v>
+        <v>焦点</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>seventy</v>
       </c>
       <c r="B29" t="str">
-        <v>focus</v>
+        <v>/ˈsevnti/</v>
       </c>
       <c r="C29" t="str">
-        <v>焦点</v>
+        <v>n./adj./num.</v>
       </c>
       <c r="D29" t="str">
-        <v>focus(焦点)📢</v>
+        <v>七十</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>lower</v>
       </c>
       <c r="B30" t="str">
-        <v>seventy</v>
+        <v>/'loər/</v>
       </c>
       <c r="C30" t="str">
-        <v>七十</v>
+        <v>vt./vi./adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>seventy(七十)📢</v>
+        <v>较低的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>milk</v>
       </c>
       <c r="B31" t="str">
-        <v>lower</v>
+        <v>/mɪlk/</v>
       </c>
       <c r="C31" t="str">
-        <v>较低的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>lower(较低的)📢</v>
+        <v>牛奶</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>pole</v>
       </c>
       <c r="B32" t="str">
-        <v>milk</v>
+        <v>/poʊl/</v>
       </c>
       <c r="C32" t="str">
-        <v>牛奶</v>
+        <v>n./vt.</v>
       </c>
       <c r="D32" t="str">
-        <v>milk(牛奶)📢</v>
+        <v>杆</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>fuel</v>
       </c>
       <c r="B33" t="str">
-        <v>pole</v>
+        <v>/ˈfjuːəl/</v>
       </c>
       <c r="C33" t="str">
-        <v>杆</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>pole(杆)📢</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>fuel</v>
-      </c>
-      <c r="C34" t="str">
         <v>燃料</v>
-      </c>
-      <c r="D34" t="str">
-        <v>fuel(燃料)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
   </ignoredErrors>
 </worksheet>
 </file>